--- a/my-bus-system/Drivers_Info.xlsx
+++ b/my-bus-system/Drivers_Info.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Wenyi\H_Bus\my-bus-system\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026Cody\H_Bus2\my-bus-system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EAB865-2DAE-4500-AF4B-331F6049D8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C29ED3-BB56-449F-90FB-E54377978DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11385" xr2:uid="{2C025831-CD2B-4E84-9750-0943CDF70825}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15600" xr2:uid="{2C025831-CD2B-4E84-9750-0943CDF70825}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -19,15 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
